--- a/Indomie Clients Details/Jalal Sons/Jalal Sons DHA.xlsx
+++ b/Indomie Clients Details/Jalal Sons/Jalal Sons DHA.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA1B3057-9E9E-4156-B563-F5BF84015B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF226024-B3B5-43B6-A9E4-7F7DD8A7D899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3333,7 +3333,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -3361,7 +3361,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -4554,7 +4554,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -4582,7 +4582,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -5775,7 +5775,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -5803,7 +5803,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -6996,7 +6996,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -7024,7 +7024,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -8217,7 +8217,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -8245,7 +8245,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -9438,7 +9438,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -9466,7 +9466,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -10656,7 +10656,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -10684,7 +10684,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -11873,7 +11873,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -11901,7 +11901,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -13090,7 +13090,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -13118,7 +13118,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -14307,7 +14307,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -14335,7 +14335,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -18274,7 +18274,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -18302,7 +18302,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -19491,7 +19491,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -19519,7 +19519,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -20708,7 +20708,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -20736,7 +20736,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -21925,7 +21925,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -21953,7 +21953,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23147,7 +23147,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -23175,7 +23175,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -24614,7 +24614,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -24642,7 +24642,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -25849,7 +25849,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -25877,7 +25877,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -27070,7 +27070,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -27098,7 +27098,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -28290,7 +28290,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -28318,7 +28318,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -29511,7 +29511,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -29539,7 +29539,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -30732,7 +30732,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -30760,7 +30760,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
